--- a/data/daily/2026-09/2026-09-10.xlsx
+++ b/data/daily/2026-09/2026-09-10.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,110 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,207 +1425,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>간편한 복용과 휴대성 — 하루 하나씩 간편하게 챙겨 먹기 좋고 휴대 부담이 없음</t>
+          <t>편리한 일일 섭취 — 하루 한 병씩 간편하게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 센스 있고 실용적이어서 선물받은 사람의 만족도가 높음</t>
+          <t>부담 없는 7입 구성 — 7개 구성으로 먼저 가볍게 먹어보고 경험하기 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 구성 — 맛이 괜찮고 7입 구성이라 가볍게 경험해 보기 좋음</t>
+          <t>거부감 없는 맛 — 맛이 괜찮고 중독성이 있어 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,28 +2655,24 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15345</v>
+        <v>15347</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>맛있는 과일향 액상 — 역한 냄새 없이 파인애플 향 액상이라 맛있게 목 넘김이 가능함</t>
+          <t>빠른 피로 회복 — 피곤하고 힘들 때 복용 시 체력이 올라오고 눈이 떠지는 기분임</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 효과 — 피로할 때 섭취 시 눈이 뜨이고 활력이 생기는 것을 체감함</t>
+          <t>역하지 않은 과일맛 — 비타민 특유의 역한 냄새가 없고 파인애플 맛이 나 맛있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>알찬 올인원 구성 — 알약과 액상을 한 번에 간편하게 삼킬 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 영양 성분이 많아 정제의 크기가 다소 큰 편임</t>
-        </is>
-      </c>
+          <t>부드러운 목넘김 — 알약 크기와 액상 제형 모두 목 넘기기가 편함</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2722,18 +2718,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 피로감이 줄어들고 아침에 가뿐하게 일어날 수 있음</t>
+          <t>확실한 피로 개선 — 복용 후 피로감이 줄어들고 아침에 가뿐해짐</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 고급스럽게 잘 되어 선물 및 응원용으로 적합함</t>
+          <t>고급스러운 포장 — 포장이 고급스럽게 잘 되어 있어 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>당뇨 환자 섭취 유의 — 당 함유 등으로 인해 당뇨가 있는 경우 직접 섭취에 주의가 필요함</t>
+          <t>기저질환자 주의 — 당뇨 등 기저질환이 있는 경우 섭취 시 주의가 필요함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2777,21 +2773,21 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8689</v>
+        <v>8690</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>휴대하기 편한 소용량 — 가방에 들어가는 사이즈라 외출 시 챙겨 다니기 용이함</t>
+          <t>신속한 체력 회복 — 피곤하거나 힘든 시험기간에 먹으면 체력이 회복되는 기분임</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>빠른 배송과 저렴한 가격 — 배송이 빠르고 가격 대비 구성 및 효능 만족도가 높음</t>
+          <t>뛰어난 휴대성 — 가방에 쏙 들어가는 사이즈로 외출 시 챙기기 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>체력 보충 및 피로 개선 — 시험기간이나 피로할 때 체력을 보충해 주는 느낌을 받음</t>
+          <t>저렴한 구매 가격 — 가격이 저렴하고 배송이 빠르게 완료됨</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2840,25 +2836,21 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>상큼하고 쫄깃한 식감 — 맛이 상큼하고 식감이 쫄깃하여 부담 없이 섭취 가능함</t>
+          <t>맛있는 젤리 제형 — 상큼하고 쫄깃하여 젤리처럼 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>센스 있는 키캡 증정 — 함께 증정되는 키캡과 귀여운 선물 포장 덕분에 기분이 좋아짐</t>
+          <t>귀여운 포장과 굿즈 — 선물 포장이 귀엽고 동봉된 키캡 사은품 만족도가 높음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 젤리가 다소 쫄깃하여 조금 더 말랑했으면 좋겠다는 의견이 있음</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>증정품 로고 디자인 아쉬움 — 키캡 뒷면에 로고가 적혀 있어 디자인적으로 약간의 아쉬움이 있음</t>
-        </is>
-      </c>
+          <t>단단한 식감 아쉬움 — 젤리 식감이 조금 더 말랑말랑했으면 하는 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -2903,17 +2895,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>넉넉한 30병 대용량 — 수량이 30병으로 넉넉하여 오랫동안 챙겨 먹기 좋음</t>
+          <t>넉넉한 30병 용량 — 다른 제품 대비 30개입으로 수량이 넉넉해 온 가족이 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>거부감 없는 향과 맛 — 향과 맛에 거부감이 없어 청소년부터 온 가족이 마시기 편함</t>
+          <t>간편한 휴대성 — 한 병씩 간편하게 휴대하며 마시기 용이함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 섭취 편의 — 출장이나 출근 시 한 병씩 휴대하며 간편하게 마시기 좋음</t>
+          <t>거부감 없는 맛 — 향과 맛에 거부감이 없어 아이들도 잘 먹음</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2962,12 +2954,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>예쁜 선물용 포장 — 선물 포장이 예쁘게 되어 있어 부담 없이 주고받기 좋음</t>
+          <t>정성스러운 선물 포장 — 선물 포장이 예쁘게 되어 있어 주고받기 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>간편한 섭취와 빠른 배송 — 배송이 빠르고 간편하게 먹을 수 있어 피로할 때 챙기기 좋음</t>
+          <t>피로 회복 효과 — 피곤할 때 먹으면 건강해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -3017,22 +3009,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>신선한 분말 액상 혼합 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 타입이라 신선함</t>
+          <t>독특한 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 타입이라 신선함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 활력 충전 — 음료수처럼 맛이 좋고 섭취 후 피로 회복 및 활력 충전에 도움 됨</t>
+          <t>고급스러운 패키지 — 포장이 예쁘고 고급스러워 선물용으로 만족스러움</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 포장이 고급스럽고 쇼핑백 및 추가 증정이 있어 선물용으로 우수함</t>
+          <t>음료 같은 맛 — 음료수처럼 맛이 부드럽고 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>생각보다 묵직한 제품 용기 — 제품 패키지와 용기 크기가 생각보다 크고 묵직한 편임</t>
+          <t>묵직한 큼직한 크기 — 생각보다 제품 크기가 크고 묵직함</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3080,18 +3072,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>간편한 피로 회복 부스터 — 피곤할 때 매일 챙겨 먹기 좋고 체력을 올려주는 부스터 역할을 함</t>
+          <t>간편한 영양 섭취 — 매일 하나씩 간편하게 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>귀엽고 따뜻한 선물 — 깜찍한 구성으로 선물받았을 때 감동과 따뜻함을 느낄 수 있음</t>
+          <t>에너지 충전 효과 — 피곤할 때 몸에 부스터 역할을 해주어 힘이 남</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>아쉬운 용량 및 수량 — 5입 구성으로 지속적으로 먹기에는 수량이 다소 적게 느껴짐</t>
+          <t>아쉬운 용량 구성 — 5입 구성으로 지속적인 관리를 위해 추가 구매가 필요함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3139,17 +3131,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤 올인원 케어 — 필요한 영양소를 한 번에 챙길 수 있어 피로함이 줄어듦</t>
+          <t>올인원 영양 케어 — 필요한 영양소를 한 번에 케어할 수 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 복용 편의 — 하루 하나씩 챙겨 먹기 편하고 휴대하기 용이함</t>
+          <t>피로감 완화 효과 — 하루 하나씩 복용 시 피로함이 덜해짐</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>깔끔한 포장과 빠른 배송 — 디자인과 포장이 깔끔하여 선물용으로 성의가 있어 보임</t>
+          <t>우수한 포장과 휴대성 — 포장이 깔끔하며 하나씩 챙겨 다니기 편함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3191,13 +3183,21 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>맛있는 베리말차맛 — 이름 그대로 베리맛과 말차맛이 어우러져 맛있음</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>알찬 사은품 구성 — 포토카드 및 단백질바 등 구성품 혜택이 우수함</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
@@ -3245,20 +3245,16 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 은은한 핑크빛 오간자 포장이 고급스러워 선물 받는 기분이 좋음</t>
+          <t>고급스러운 선물 포장 — 은은하고 고급스러운 핑크빛 포장으로 선물받는 기분이 좋음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>알찬 추가 증정 구성 — 추가 증정 앰플 및 샘플이 들어 있어 구성이 알참</t>
+          <t>피부 개선 기대감 — 꾸준히 먹으면 피부가 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>즉각적인 효과 미비 — 복용 초반에는 효과를 바로 체감하기 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3304,22 +3300,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다양하여 매일 먹어도 물리지 않음</t>
+          <t>뛰어난 가성비 — 24개 수량을 저렴한 가격으로 구매할 수 있음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 구성 — 24팩 기준 가격이 매우 저렴하여 다이어트 식단으로 경제적임</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>간편한 전자레인지 조리 — 전자레인지 조리로 간편하고 손쉽게 식단 관리가 가능함</t>
-        </is>
-      </c>
+          <t>질리지 않는 양념맛 — 뻑뻑함이 적고 자극적이지 않은 다양한 양념이라 물리지 않음</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서 배송되는 경우가 발생함</t>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아서 도착하는 경우가 발생함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3367,22 +3359,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>다채로운 맛과 종류 — 종류가 다양하여 골라 먹는 재미가 있고 전반적으로 맛이 우수함</t>
+          <t>다양한 맛 구성 — 종류가 많아 매일 골라 먹는 재미가 있고 식단 관리로 좋음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>저렴한 대용량 패키지 — 할인 혜택으로 30팩 대용량을 저렴한 가격에 구매 가능함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>증정 보냉백의 실용성 — 함께 제공되는 보냉 파우치 덕분에 도시락 챙길 때 유용함</t>
-        </is>
-      </c>
+          <t>유용한 보냉백 증정 — 보냉 파우치가 증정되어 도시락을 싸 다닐 때 편리함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>배송 시 해동 아쉬움 — 배송을 받았을 때 제품이 많이 녹아있는 상태로 도착함</t>
+          <t>배송 시 제품 해동 — 배송 도중 제품이 많이 녹아 오는 경우가 있음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -3430,17 +3418,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없고 일반 음료처럼 맛있음</t>
+          <t>비리지 않고 깔끔한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛없이 달콤하고 깔끔함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>속 편한 포만감 제공 — 마신 후 속이 더부룩하지 않으며 간식 대용으로 허기를 채우기 좋음</t>
+          <t>속 편한 포만감 — 마신 뒤 속이 더부룩하지 않고 가볍게 허기를 채우기 좋음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 운동 후 챙겨 마시기 편함</t>
+          <t>슬림한 휴대용 용기 — 패키지가 슬림해서 가방에 넣어 다니며 간편하게 섭취하기 편함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -3489,17 +3477,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부담 없는 복용 방식 — 물이나 음료에 타서 부담 없이 매일 챙겨 먹기 편함</t>
+          <t>확실한 운동 효과 — 꾸준히 먹으면 몸이 커지는 느낌과 득근 효과를 얻을 수 있음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>귀여운 키링 증정 — 제품과 함께 동봉되어 오는 키링이 귀여워서 만족스러움</t>
+          <t>부담 없는 섭취 방식 — 물이나 음료에 쉽게 타서 먹을 수 있음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>입문용에 적합한 용량 — 크레아틴을 처음 접할 때 부담 없이 시도하기 좋은 용량 크기임</t>
+          <t>귀여운 증정 키링 — 함께 동봉되는 키링이 귀엽고 만족스러움</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3548,17 +3536,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 군고구마 맛처럼 고소하여 부담 없이 맛있게 먹을 수 있음</t>
+          <t>속 편한 소화 개선 — 식후 답답하고 더부룩한 속을 편안하게 해줌</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>우수한 소화 및 속 편함 — 식후 더부룩함이 줄어들고 소화 및 배변 활동에 도움이 됨</t>
+          <t>고소한 군고구마맛 — 군고구마 맛이 나며 고소하여 부담 없이 먹을 수 있음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>풍성한 사은품과 혜택 — 행사 시 사은품이 많이 제공되고 저렴하게 구매할 수 있음</t>
+          <t>원활한 배변 활동 — 매일 섭취 시 배변 활동을 원활하게 돕음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3607,17 +3595,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>초고함량 및 빠른 체감 — 6,200mg 고함량으로 피로 회복과 운동 집중력 향상에 효과적임</t>
+          <t>고함량 아르기닌 — 1포당 L-아르기닌 6,200mg 함유로 확실한 함량을 제공함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>개별 포장의 뛰어난 휴대성 — 개별 포장된 스틱 타입으로 외출이나 운동 전 꺼내 먹기 편함</t>
+          <t>활력 및 컨디션 증진 — 섭취 후 기력이 올라가고 운동 지구력 및 집중력이 좋아짐</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 전용 쇼핑백과 추가 스틱 증정이 포함되어 선물용으로 매우 좋음</t>
+          <t>고급 쇼핑백과 증정품 — 전용 쇼핑백과 추가 샘플 포가 증정되어 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3627,7 +3615,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3635,50 +3623,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1534</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>알약 형태의 간편함 — 알약 타입이라 챙겨 먹기 깔끔하고 간편함</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>알찬 영양제 세트 구성 — 아르기닌과 밀크씨슬(마카) 조합으로 넉넉하게 건강 관리가 가능함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>체감되는 활력 개선 — 복용 후 몸이 덜 무겁고 하루를 시작하는 에너지가 달라짐</t>
-        </is>
-      </c>
+          <t>탁월한 숙취 해소 — 복용 시 숙취 해소 효과가 매우 뛰어남</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3725,19 +3705,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 레몬맛 액상 스틱이라 물에 쉽게 타서 부담 없이 먹기 좋음</t>
+          <t>상큼한 레몬맛 액상 — 액상 타입이라 물에 타 먹기 편하고 레몬맛이라 맛에 부담이 없음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>전용 케이스 동봉 — 케이스가 함께 동봉되어 외출 시 챙겨 다니기 용이함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>초고함량 7000mg — 고함량 아르기닌 함유로 피로 회복과 운동 시 도움을 줌</t>
-        </is>
-      </c>
+          <t>공복 피로 회복 체감 — 아침 공복 복용 시 하루 시작이 가벼워지고 피로 회복에 도움 됨</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4063,13 +4039,13 @@
         <v>16004</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15345</v>
+        <v>15347</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3342</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8689</v>
+        <v>8690</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>6450</v>
@@ -4098,105 +4074,100 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복용과 휴대성 — 하루 하나씩 간편하게 챙겨 먹기 좋고 휴대 부담이 없음
-선물용으로 높은 만족도 — 센스 있고 실용적이어서 선물받은 사람의 만족도가 높음
-부담 없는 맛과 구성 — 맛이 괜찮고 7입 구성이라 가볍게 경험해 보기 좋음</t>
+          <t>편리한 일일 섭취 — 하루 한 병씩 간편하게 챙겨 먹기 편함
+부담 없는 7입 구성 — 7개 구성으로 먼저 가볍게 먹어보고 경험하기 좋음
+거부감 없는 맛 — 맛이 괜찮고 중독성이 있어 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일향 액상 — 역한 냄새 없이 파인애플 향 액상이라 맛있게 목 넘김이 가능함
-빠른 피로 회복 효과 — 피로할 때 섭취 시 눈이 뜨이고 활력이 생기는 것을 체감함
-알찬 올인원 구성 — 알약과 액상을 한 번에 간편하게 삼킬 수 있어 만족스러움</t>
+          <t>빠른 피로 회복 — 피곤하고 힘들 때 복용 시 체력이 올라오고 눈이 떠지는 기분임
+역하지 않은 과일맛 — 비타민 특유의 역한 냄새가 없고 파인애플 맛이 나 맛있음
+부드러운 목넘김 — 알약 크기와 액상 제형 모두 목 넘기기가 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 피로감이 줄어들고 아침에 가뿐하게 일어날 수 있음
-고급스러운 선물 포장 — 포장이 고급스럽게 잘 되어 선물 및 응원용으로 적합함</t>
+          <t>확실한 피로 개선 — 복용 후 피로감이 줄어들고 아침에 가뿐해짐
+고급스러운 포장 — 포장이 고급스럽게 잘 되어 있어 선물용으로 적합함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>휴대하기 편한 소용량 — 가방에 들어가는 사이즈라 외출 시 챙겨 다니기 용이함
-빠른 배송과 저렴한 가격 — 배송이 빠르고 가격 대비 구성 및 효능 만족도가 높음
-체력 보충 및 피로 개선 — 시험기간이나 피로할 때 체력을 보충해 주는 느낌을 받음</t>
+          <t>신속한 체력 회복 — 피곤하거나 힘든 시험기간에 먹으면 체력이 회복되는 기분임
+뛰어난 휴대성 — 가방에 쏙 들어가는 사이즈로 외출 시 챙기기 편함
+저렴한 구매 가격 — 가격이 저렴하고 배송이 빠르게 완료됨</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 쫄깃한 식감 — 맛이 상큼하고 식감이 쫄깃하여 부담 없이 섭취 가능함
-센스 있는 키캡 증정 — 함께 증정되는 키캡과 귀여운 선물 포장 덕분에 기분이 좋아짐</t>
+          <t>맛있는 젤리 제형 — 상큼하고 쫄깃하여 젤리처럼 부담 없이 먹기 좋음
+귀여운 포장과 굿즈 — 선물 포장이 귀엽고 동봉된 키캡 사은품 만족도가 높음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>넉넉한 30병 대용량 — 수량이 30병으로 넉넉하여 오랫동안 챙겨 먹기 좋음
-거부감 없는 향과 맛 — 향과 맛에 거부감이 없어 청소년부터 온 가족이 마시기 편함
-우수한 휴대성과 섭취 편의 — 출장이나 출근 시 한 병씩 휴대하며 간편하게 마시기 좋음</t>
+          <t>넉넉한 30병 용량 — 다른 제품 대비 30개입으로 수량이 넉넉해 온 가족이 먹기 좋음
+간편한 휴대성 — 한 병씩 간편하게 휴대하며 마시기 용이함
+거부감 없는 맛 — 향과 맛에 거부감이 없어 아이들도 잘 먹음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>예쁜 선물용 포장 — 선물 포장이 예쁘게 되어 있어 부담 없이 주고받기 좋음
-간편한 섭취와 빠른 배송 — 배송이 빠르고 간편하게 먹을 수 있어 피로할 때 챙기기 좋음</t>
+          <t>정성스러운 선물 포장 — 선물 포장이 예쁘게 되어 있어 주고받기 좋음
+피로 회복 효과 — 피곤할 때 먹으면 건강해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>신선한 분말 액상 혼합 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 타입이라 신선함
-부담 없는 맛과 활력 충전 — 음료수처럼 맛이 좋고 섭취 후 피로 회복 및 활력 충전에 도움 됨
-고급스러운 패키지 — 포장이 고급스럽고 쇼핑백 및 추가 증정이 있어 선물용으로 우수함</t>
+          <t>독특한 혼합 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 마시는 타입이라 신선함
+고급스러운 패키지 — 포장이 예쁘고 고급스러워 선물용으로 만족스러움
+음료 같은 맛 — 음료수처럼 맛이 부드럽고 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>간편한 피로 회복 부스터 — 피곤할 때 매일 챙겨 먹기 좋고 체력을 올려주는 부스터 역할을 함
-귀엽고 따뜻한 선물 — 깜찍한 구성으로 선물받았을 때 감동과 따뜻함을 느낄 수 있음</t>
+          <t>간편한 영양 섭취 — 매일 하나씩 간편하게 챙겨 먹기 좋음
+에너지 충전 효과 — 피곤할 때 몸에 부스터 역할을 해주어 힘이 남</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 올인원 케어 — 필요한 영양소를 한 번에 챙길 수 있어 피로함이 줄어듦
-우수한 휴대성과 복용 편의 — 하루 하나씩 챙겨 먹기 편하고 휴대하기 용이함
-깔끔한 포장과 빠른 배송 — 디자인과 포장이 깔끔하여 선물용으로 성의가 있어 보임</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>올인원 영양 케어 — 필요한 영양소를 한 번에 케어할 수 있음
+피로감 완화 효과 — 하루 하나씩 복용 시 피로함이 덜해짐
+우수한 포장과 휴대성 — 포장이 깔끔하며 하나씩 챙겨 다니기 편함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 영양 성분이 많아 정제의 크기가 다소 큰 편임</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>당뇨 환자 섭취 유의 — 당 함유 등으로 인해 당뇨가 있는 경우 직접 섭취에 주의가 필요함</t>
+          <t>기저질환자 주의 — 당뇨 등 기저질환이 있는 경우 섭취 시 주의가 필요함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>다소 단단한 젤리 식감 — 젤리가 다소 쫄깃하여 조금 더 말랑했으면 좋겠다는 의견이 있음
-증정품 로고 디자인 아쉬움 — 키캡 뒷면에 로고가 적혀 있어 디자인적으로 약간의 아쉬움이 있음</t>
+          <t>단단한 식감 아쉬움 — 젤리 식감이 조금 더 말랑말랑했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>생각보다 묵직한 제품 용기 — 제품 패키지와 용기 크기가 생각보다 크고 묵직한 편임</t>
+          <t>묵직한 큼직한 크기 — 생각보다 제품 크기가 크고 묵직함</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 용량 및 수량 — 5입 구성으로 지속적으로 먹기에는 수량이 다소 적게 느껴짐</t>
+          <t>아쉬운 용량 구성 — 5입 구성으로 지속적인 관리를 위해 추가 구매가 필요함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4437,7 +4408,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4494,7 +4465,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4551,7 +4522,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4567,7 +4538,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>4</v>
@@ -4604,7 +4575,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>731</v>
@@ -4628,7 +4599,7 @@
         <v>248</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1534</v>
+        <v>1</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>38</v>
@@ -4640,67 +4611,67 @@
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 베리말차맛 — 이름 그대로 베리맛과 말차맛이 어우러져 맛있음
+알찬 사은품 구성 — 포토카드 및 단백질바 등 구성품 혜택이 우수함</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 은은한 핑크빛 오간자 포장이 고급스러워 선물 받는 기분이 좋음
-알찬 추가 증정 구성 — 추가 증정 앰플 및 샘플이 들어 있어 구성이 알참</t>
+          <t>고급스러운 선물 포장 — 은은하고 고급스러운 핑크빛 포장으로 선물받는 기분이 좋음
+피부 개선 기대감 — 꾸준히 먹으면 피부가 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>다양한 맛과 부드러운 식감 — 뻑뻑함이 적고 맛이 다양하여 매일 먹어도 물리지 않음
-뛰어난 가성비와 구성 — 24팩 기준 가격이 매우 저렴하여 다이어트 식단으로 경제적임
-간편한 전자레인지 조리 — 전자레인지 조리로 간편하고 손쉽게 식단 관리가 가능함</t>
+          <t>뛰어난 가성비 — 24개 수량을 저렴한 가격으로 구매할 수 있음
+질리지 않는 양념맛 — 뻑뻑함이 적고 자극적이지 않은 다양한 양념이라 물리지 않음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 맛과 종류 — 종류가 다양하여 골라 먹는 재미가 있고 전반적으로 맛이 우수함
-저렴한 대용량 패키지 — 할인 혜택으로 30팩 대용량을 저렴한 가격에 구매 가능함
-증정 보냉백의 실용성 — 함께 제공되는 보냉 파우치 덕분에 도시락 챙길 때 유용함</t>
+          <t>다양한 맛 구성 — 종류가 많아 매일 골라 먹는 재미가 있고 식단 관리로 좋음
+유용한 보냉백 증정 — 보냉 파우치가 증정되어 도시락을 싸 다닐 때 편리함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없고 일반 음료처럼 맛있음
-속 편한 포만감 제공 — 마신 후 속이 더부룩하지 않으며 간식 대용으로 허기를 채우기 좋음
-슬림한 용기의 높은 휴대성 — 패키지가 슬림하여 가방에 넣고 다니며 운동 후 챙겨 마시기 편함</t>
+          <t>비리지 않고 깔끔한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛없이 달콤하고 깔끔함
+속 편한 포만감 — 마신 뒤 속이 더부룩하지 않고 가볍게 허기를 채우기 좋음
+슬림한 휴대용 용기 — 패키지가 슬림해서 가방에 넣어 다니며 간편하게 섭취하기 편함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 복용 방식 — 물이나 음료에 타서 부담 없이 매일 챙겨 먹기 편함
-귀여운 키링 증정 — 제품과 함께 동봉되어 오는 키링이 귀여워서 만족스러움
-입문용에 적합한 용량 — 크레아틴을 처음 접할 때 부담 없이 시도하기 좋은 용량 크기임</t>
+          <t>확실한 운동 효과 — 꾸준히 먹으면 몸이 커지는 느낌과 득근 효과를 얻을 수 있음
+부담 없는 섭취 방식 — 물이나 음료에 쉽게 타서 먹을 수 있음
+귀여운 증정 키링 — 함께 동봉되는 키링이 귀엽고 만족스러움</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 풍미 — 군고구마 맛처럼 고소하여 부담 없이 맛있게 먹을 수 있음
-우수한 소화 및 속 편함 — 식후 더부룩함이 줄어들고 소화 및 배변 활동에 도움이 됨
-풍성한 사은품과 혜택 — 행사 시 사은품이 많이 제공되고 저렴하게 구매할 수 있음</t>
+          <t>속 편한 소화 개선 — 식후 답답하고 더부룩한 속을 편안하게 해줌
+고소한 군고구마맛 — 군고구마 맛이 나며 고소하여 부담 없이 먹을 수 있음
+원활한 배변 활동 — 매일 섭취 시 배변 활동을 원활하게 돕음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 및 빠른 체감 — 6,200mg 고함량으로 피로 회복과 운동 집중력 향상에 효과적임
-개별 포장의 뛰어난 휴대성 — 개별 포장된 스틱 타입으로 외출이나 운동 전 꺼내 먹기 편함
-고급스러운 선물 구성 — 전용 쇼핑백과 추가 스틱 증정이 포함되어 선물용으로 매우 좋음</t>
+          <t>고함량 아르기닌 — 1포당 L-아르기닌 6,200mg 함유로 확실한 함량을 제공함
+활력 및 컨디션 증진 — 섭취 후 기력이 올라가고 운동 지구력 및 집중력이 좋아짐
+고급 쇼핑백과 증정품 — 전용 쇼핑백과 추가 샘플 포가 증정되어 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>알약 형태의 간편함 — 알약 타입이라 챙겨 먹기 깔끔하고 간편함
-알찬 영양제 세트 구성 — 아르기닌과 밀크씨슬(마카) 조합으로 넉넉하게 건강 관리가 가능함
-체감되는 활력 개선 — 복용 후 몸이 덜 무겁고 하루를 시작하는 에너지가 달라짐</t>
+          <t>탁월한 숙취 해소 — 복용 시 숙취 해소 효과가 매우 뛰어남</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 레몬맛 액상 스틱이라 물에 쉽게 타서 부담 없이 먹기 좋음
-전용 케이스 동봉 — 케이스가 함께 동봉되어 외출 시 챙겨 다니기 용이함
-초고함량 7000mg — 고함량 아르기닌 함유로 피로 회복과 운동 시 도움을 줌</t>
+          <t>상큼한 레몬맛 액상 — 액상 타입이라 물에 타 먹기 편하고 레몬맛이라 맛에 부담이 없음
+공복 피로 회복 체감 — 아침 공복 복용 시 하루 시작이 가벼워지고 피로 회복에 도움 됨</t>
         </is>
       </c>
     </row>
@@ -4711,19 +4682,15 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>즉각적인 효과 미비 — 복용 초반에는 효과를 바로 체감하기 어려울 수 있음</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 문제 — 배송 과정에서 제품이 완전히 녹아서 배송되는 경우가 발생함</t>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아서 도착하는 경우가 발생함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 해동 아쉬움 — 배송을 받았을 때 제품이 많이 녹아있는 상태로 도착함</t>
+          <t>배송 시 제품 해동 — 배송 도중 제품이 많이 녹아 오는 경우가 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -4781,7 +4748,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4976,7 +4943,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4984,43 +4951,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>628</v>
+        <v>4496</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 5포 소용량 구성으로 가격 부담 없이 구매하여 먹기 좋음</t>
+          <t>식후 디저트 욕구 감소 — 식사 후 복용하면 디저트가 당기지 않아 관리에 유용함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>취향별 다양한 복용 — 쓰지 않아서 얼음과 함께 시원하게 마시거나 데워 먹기 좋음</t>
+          <t>편리한 복용법 — 간편하게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5031,7 +4998,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5039,12 +5006,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5054,28 +5021,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1480</v>
+        <v>6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>컴팩트한 용기 사이즈 — 보관 용기가 매우 작아 가방에 들고 다니며 챙기기 좋음</t>
+          <t>고급스러운 패키지 — 가격 대비 패키지가 알차고 고급스러워 명절 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>작은 캡슐 크기와 목넘김 — 캡슐 크기가 작아 목 넘김이 편하고 소화가 잘 됨</t>
+          <t>부담 없는 환 제형 — 쓴맛이 심하지 않고 환 크기가 적당해 씹어 삼키기 편함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -5086,7 +5053,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5094,7 +5061,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5109,26 +5076,30 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>6080</v>
+        <v>6175</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>무난한 데일리 복용 — 아침 식후마다 매일 간편하게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>매우 뛰어난 가성비 — 타 판매처 대비 저렴하여 싸게 건강을 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>편리한 휴대성 — 사이즈가 적당하여 휴대하고 다니며 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -5145,49 +5116,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2238</v>
+        <v>986</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>달콤한 파인애플 맛 — 비타민 캔디처럼 달콤하고 맛있어 간식처럼 먹기 좋음</t>
+          <t>편리한 개별 포장 — 1포씩 개별 포장되어 있어 들고 다니며 먹기 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>저렴한 구매 가격 — 저렴하게 챙겨 먹기 좋은 붓기 캔디 제품임</t>
+          <t>체험용 좋은 가성비 — 가성비가 좋아 대용량 구매 전 체험해보기 적합함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>미비한 붓기 제거 효과 — 붓기가 드라마틱하게 빠지는 효과는 체감하기 어려움</t>
+          <t>아쉬운 맛과 향 — 맛이 부족하고 향에 민감한 사람에게는 추천하지 않음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -5196,7 +5167,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5204,12 +5175,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>판티오</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5219,28 +5190,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991021&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/xVYROwLnuZYLoqWwcjU6033991021_00_00xVYROwLnuZYLoqWwcjU6.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>6170</v>
+        <v>140</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>타사 대비 저렴한 가격 — 다른 곳보다 가격이 싸서 가성비 좋게 건강을 챙길 수 있음</t>
+          <t>간편한 휴대 복용 — 바쁜 날에도 간편하게 휴대하며 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>전문가 추천 제품 — 약사들이 추천하는 영상이나 추천으로 신뢰를 얻음</t>
+          <t>식단 관리 심리적 안심 — 다이어트 시 체중 유지에 도움이 되고 마음이 든든함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5251,7 +5222,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5259,12 +5230,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5274,34 +5245,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000138&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0buLkRj5uSU3KVXDKEhY600000138_00_000buLkRj5uSU3KVXDKEhY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1268</v>
+        <v>11</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>압도적인 초저가 가성비 — 5,000원에 한 달 분량을 구매할 수 있어 가성비가 훌륭함</t>
+          <t>쫀득한 식감과 편의성 — 개별 용기 포장으로 꺼내 먹기 편하고 쫀득해서 씹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>편리한 복용과 빠른 배송 — 먹기도 편하고 배송이 빠름</t>
+          <t>피로 개선 효과 — 섭취 후 기력 보충이 되고 피로감이 덜함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>미비한 초기 체감 효능 — 단기간 복용 시에는 효능을 명확히 체감하기 어려움</t>
+          <t>박스 가격표 인쇄 — 박스에 가격표가 인쇄되어 있어 선물용 시 노출이 신경 쓰임</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -5310,7 +5281,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5318,12 +5289,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5333,43 +5304,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1897</v>
+        <v>6085</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 소용량 시도 — 10포 구성이라 영양제가 떨어졌을 때 급하게 사거나 입문용으로 좋음</t>
+          <t>쉬운 구매 접근성 — 매장에서 쉽게 구할 수 있어 구매가 용이함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>전문의 추천 영양 성분 — 산부인과 교수의 권유 등으로 여성 건강에 챙겨 먹기 좋음</t>
+          <t>체감되는 효능 — 꾸준히 복용 시 효능을 체감할 수 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>대량 구매 시 아쉬운 가격 — 여러 개를 지속해서 구매하기에는 단위당 가성비가 떨어짐</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5377,58 +5344,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 더채움 비오틴 하루구미 30일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/mhxyGp5yOjC4MHfaY2J8613602127_00_01mhxyGp5yOjC4MHfaY2J8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>679</v>
+        <v>3820</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>맛있는 복숭아맛 구미 — 복숭아 맛 구미 형태로 과자 대신 간식처럼 즐기기 좋음</t>
+          <t>우수한 가성비 — 가격 대비 구성과 효과가 좋아 지속 재구매함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>가격 대비 훌륭한 성분 — 저렴한 가격임에도 영양 성분 구성이 알참</t>
+          <t>핵심 성분 집중 — 불필요한 성분 없이 눈 관리에 필요한 요소가 충실함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>불명확한 효능 체감 — 맛은 있으나 영양제로서의 뚜렷한 효과 체감은 아쉬움</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5436,12 +5399,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5451,32 +5414,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1465</v>
+        <v>1899</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>식물성 오메가3 가성비 — 식물성 제품임에도 직구 제품보다 가격이 저렴하여 가성비가 좋음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>체감되는 혈액 순환 — 복용 시 몸의 혈액 순환이 좋아지는 느낌을 받음</t>
-        </is>
-      </c>
+          <t>적절한 소량 구성 — 기존 약이 떨어졌거나 처음 시도할 때 소량 구매하기 적합함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>대량 구매 시 가성비 — 여러 개를 지속해서 구매하기에는 가성비가 떨어질 수 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -5491,12 +5454,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5506,34 +5469,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032640075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/0RECqyOK2V8qTztn2K7E032640075_00_000RECqyOK2V8qTztn2K7E.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>986</v>
+        <v>188</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>개별 스틱 포장의 편의성 — 10포씩 개별 포장되어 있어 휴대 및 사용이 매우 편리함</t>
+          <t>맛있는 풍미 — 맛이 좋아 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>부담 없는 체험용 수량 — 대용량을 사기 전 맛이나 품질을 미리 체험해 보기 좋음</t>
+          <t>가격 대비 만족감 — 전반적인 품질 대비 만족도가 높음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>호불호 갈리는 맛과 향 — 올리브유 특유의 향이 있어 풍미에 민감할 경우 아쉬울 수 있음</t>
+          <t>가격 부담감 — 지속 복용 시 가격이 조금 더 저렴했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5650,47 +5613,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>홍삼/인삼</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5707,14 +5670,14 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>휴럼</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
@@ -5722,37 +5685,37 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>판티오</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>안국약품</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -5764,52 +5727,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[보령약국 X Pantio] 다이어트 컷 올인원 15포 15일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 콜라겐 60정 30일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 루테인 30정 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 더채움 비오틴 하루구미 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>홀베리 유기농 엑스트라버진 올리브유 10포</t>
+          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5795,7 @@
         <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5841,13 +5804,13 @@
         <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5857,34 +5820,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>628</v>
+        <v>4496</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1480</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6080</v>
+        <v>6175</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2238</v>
+        <v>986</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6170</v>
+        <v>140</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1268</v>
+        <v>11</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1897</v>
+        <v>6085</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>679</v>
+        <v>3820</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1465</v>
+        <v>1899</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>986</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5895,61 +5858,61 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 5포 소용량 구성으로 가격 부담 없이 구매하여 먹기 좋음
-취향별 다양한 복용 — 쓰지 않아서 얼음과 함께 시원하게 마시거나 데워 먹기 좋음</t>
+          <t>식후 디저트 욕구 감소 — 식사 후 복용하면 디저트가 당기지 않아 관리에 유용함
+편리한 복용법 — 간편하게 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>컴팩트한 용기 사이즈 — 보관 용기가 매우 작아 가방에 들고 다니며 챙기기 좋음
-작은 캡슐 크기와 목넘김 — 캡슐 크기가 작아 목 넘김이 편하고 소화가 잘 됨</t>
+          <t>고급스러운 패키지 — 가격 대비 패키지가 알차고 고급스러워 명절 선물용으로 적합함
+부담 없는 환 제형 — 쓴맛이 심하지 않고 환 크기가 적당해 씹어 삼키기 편함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>무난한 데일리 복용 — 아침 식후마다 매일 간편하게 챙겨 먹기 좋음</t>
+          <t>매우 뛰어난 가성비 — 타 판매처 대비 저렴하여 싸게 건강을 챙길 수 있음
+편리한 휴대성 — 사이즈가 적당하여 휴대하고 다니며 먹기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>달콤한 파인애플 맛 — 비타민 캔디처럼 달콤하고 맛있어 간식처럼 먹기 좋음
-저렴한 구매 가격 — 저렴하게 챙겨 먹기 좋은 붓기 캔디 제품임</t>
+          <t>편리한 개별 포장 — 1포씩 개별 포장되어 있어 들고 다니며 먹기 편함
+체험용 좋은 가성비 — 가성비가 좋아 대용량 구매 전 체험해보기 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>타사 대비 저렴한 가격 — 다른 곳보다 가격이 싸서 가성비 좋게 건강을 챙길 수 있음
-전문가 추천 제품 — 약사들이 추천하는 영상이나 추천으로 신뢰를 얻음</t>
+          <t>간편한 휴대 복용 — 바쁜 날에도 간편하게 휴대하며 챙겨 먹기 좋음
+식단 관리 심리적 안심 — 다이어트 시 체중 유지에 도움이 되고 마음이 든든함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 초저가 가성비 — 5,000원에 한 달 분량을 구매할 수 있어 가성비가 훌륭함
-편리한 복용과 빠른 배송 — 먹기도 편하고 배송이 빠름</t>
+          <t>쫀득한 식감과 편의성 — 개별 용기 포장으로 꺼내 먹기 편하고 쫀득해서 씹기 좋음
+피로 개선 효과 — 섭취 후 기력 보충이 되고 피로감이 덜함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 소용량 시도 — 10포 구성이라 영양제가 떨어졌을 때 급하게 사거나 입문용으로 좋음
-전문의 추천 영양 성분 — 산부인과 교수의 권유 등으로 여성 건강에 챙겨 먹기 좋음</t>
+          <t>쉬운 구매 접근성 — 매장에서 쉽게 구할 수 있어 구매가 용이함
+체감되는 효능 — 꾸준히 복용 시 효능을 체감할 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 복숭아맛 구미 — 복숭아 맛 구미 형태로 과자 대신 간식처럼 즐기기 좋음
-가격 대비 훌륭한 성분 — 저렴한 가격임에도 영양 성분 구성이 알참</t>
+          <t>우수한 가성비 — 가격 대비 구성과 효과가 좋아 지속 재구매함
+핵심 성분 집중 — 불필요한 성분 없이 눈 관리에 필요한 요소가 충실함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>식물성 오메가3 가성비 — 식물성 제품임에도 직구 제품보다 가격이 저렴하여 가성비가 좋음
-체감되는 혈액 순환 — 복용 시 몸의 혈액 순환이 좋아지는 느낌을 받음</t>
+          <t>적절한 소량 구성 — 기존 약이 떨어졌거나 처음 시도할 때 소량 구매하기 적합함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>개별 스틱 포장의 편의성 — 10포씩 개별 포장되어 있어 휴대 및 사용이 매우 편리함
-부담 없는 체험용 수량 — 대용량을 사기 전 맛이나 품질을 미리 체험해 보기 좋음</t>
+          <t>맛있는 풍미 — 맛이 좋아 부담 없이 섭취 가능함
+가격 대비 만족감 — 전반적인 품질 대비 만족도가 높음</t>
         </is>
       </c>
     </row>
@@ -5964,29 +5927,25 @@
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>미비한 붓기 제거 효과 — 붓기가 드라마틱하게 빠지는 효과는 체감하기 어려움</t>
+          <t>아쉬운 맛과 향 — 맛이 부족하고 향에 민감한 사람에게는 추천하지 않음</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>미비한 초기 체감 효능 — 단기간 복용 시에는 효능을 명확히 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>대량 구매 시 아쉬운 가격 — 여러 개를 지속해서 구매하기에는 단위당 가성비가 떨어짐</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>불명확한 효능 체감 — 맛은 있으나 영양제로서의 뚜렷한 효과 체감은 아쉬움</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+          <t>박스 가격표 인쇄 — 박스에 가격표가 인쇄되어 있어 선물용 시 노출이 신경 쓰임</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>대량 구매 시 가성비 — 여러 개를 지속해서 구매하기에는 가성비가 떨어질 수 있음</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 맛과 향 — 올리브유 특유의 향이 있어 풍미에 민감할 경우 아쉬울 수 있음</t>
+          <t>가격 부담감 — 지속 복용 시 가격이 조금 더 저렴했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5957,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6013,27 +5972,27 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -6230,7 +6189,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6240,39 +6199,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>6494</v>
+        <v>5570</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 복용 후 아침에 몸이 가뿐해지고 피로 체감이 달라짐</t>
+          <t>고함량 체력 끌어올림 — 3000mg 고용량으로 신맛이 강하지만 피로 개선 효과가 확실함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3000mg 고용량 섭취 — 1포로 고용량 비타민 C 3,000mg을 간편하게 섭취할 수 있음</t>
+          <t>흡수 빠른 가루 제형 — 알약 대비 흡수와 복용이 유용한 가루 형태로 구성됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>충분한 수분 섭취 필요 — 고용량 제형 특성상 결석 방지를 위해 하루 2L 이상 물을 마셔야 함</t>
+          <t>충분한 수구 섭취 필요 — 고용량 복용 특성상 결석 예방을 위해 많은 물을 마셔야 함</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -6281,7 +6240,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6289,58 +6248,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>24945</v>
+        <v>6498</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 더블 케어할 수 있어 유용함</t>
+          <t>가뿐한 아침 피로 회복 — 지속 섭취 시 아침에 몸이 가뿐해지고 피로도가 달라짐</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>초소형 캡슐의 목넘김 — 170mg의 매우 작고 가벼운 캡슐이라 물과 함께 쉽게 넘어감</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>귀여운 포켓몬 굿즈 — 포켓몬 에디션 패키지와 증정 카드케이스의 소장 가치가 높음</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>넉넉한 100일분 용량 — 100포 대용량이라 오랫동안 꾸준히 챙겨 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>수분 섭취 유의 — 부작용을 방지하기 위해 하루 2L 이상의 물 섭취가 권장됨</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6348,12 +6307,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6363,32 +6322,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216858ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3158</v>
+        <v>14774</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>부담 없는 합리적 가격 — 비싼 제품과 차이 없이 가격 부담이 적어 정착하기 좋음</t>
+          <t>빠르고 깊은 수면 유도 — 취침 전 섭취 시 잠이 확 들고 푹 자는 데 도움이 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>안전한 듀라벡 코팅 — 열과 위산에 강한 코팅 기술로 유산균이 장까지 잘 전달됨</t>
+          <t>맛있는 구미 제형 — 약이 아닌 젤리 형태로 간식처럼 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>취침 전 섭취 양치 번거로움 — 젤리 형태 특성상 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -6403,7 +6366,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6413,33 +6376,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24,320원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>24129</v>
+        <v>8078</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>체감되는 면역 및 장 건강 — 공복 복용 시 장 건강과 면역력을 관리하는 데 효과를 봄</t>
+          <t>간편한 1일 1캡슐 — 아침 공복에 물과 함께 하루 한 알로 간편하게 케어함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알찬 1+1 기획 구성 — 1+1 기획으로 2달 동안 복용 가능한 60캡슐을 확보할 수 있음</t>
+          <t>질과 장 건강 케어 — 여성 건강 기초가 되는 질유산균과 장 건강을 함께 챙김</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6458,46 +6421,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>8071</v>
+        <v>24957</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>여성용 질유산균 루틴 — 질 건강 관리를 위한 아침 공복 이너뷰티 루틴으로 적합함</t>
+          <t>소형 캡슐 목넘김 — 170mg의 매우 작은 캡슐 크기라 물과 함께 쉽게 넘어감</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>철분제 추가 증정 — 철분 헤모케어가 증정되어 추가 영양 보충이 가능함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>질과 장 더블 케어 — 식약처 인정 원료로 보장균수 50억을 충족하여 효과적임</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>귀여운 포켓몬 콜라보 — 카드케이스 증정 등 패키지가 귀여워 소장 가치가 높음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -6505,7 +6472,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6513,41 +6480,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>바이오렉트라 마그네슘 400 울트라 다이렉트</t>
+          <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>바이오렉트라</t>
+          <t>그린몬스터</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35,000원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246134&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000172168&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024613411ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017216858ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>267</v>
+        <v>3158</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>할인가 구매의 유용성 — 세일 및 쿠폰 혜택을 이용해 저렴하게 쟁여두기 좋음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>부담 없는 저렴한 가격 — 가격대가 저렴하여 꾸준히 정착해 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>듀라벡 코팅 기술 — 19종 유산균이 장까지 안전하게 전달되도록 코팅 처리됨</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6564,47 +6535,51 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>10914</v>
+        <v>41013</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>상큼한 맛과 에너지 충전 — 상큼하게 즐길 수 있어 피로할 때 활력을 채우기 좋음</t>
+          <t>즉각적인 체력 충전 — 지칠 때 하나만 챙겨 먹어도 피로 회복 효과가 확실함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>포차코 메쉬백 증정 — 귀여운 포차코 메쉬백이 포함되어 구성이 만족스러움</t>
+          <t>탄산수 활용 복용법 — 진한 액상을 탄산수에 타 마시면 상큼한 에이드처럼 즐길 수 있음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>높은 가격 부담 — 제품 품질은 좋으나 다소 비싼 가격대가 단점임</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -6619,58 +6594,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>그래니 살라 VPL정 60정(1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>그래니샐러드</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>23,500원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000253967&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025396704ko.png?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>14757</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>빠르고 깊은 수면 유도 — 자기 전 복용 시 깊고 편안하게 잠들 수 있도록 도와줌</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>제형 선택의 다양성 — 맛있는 젤리 형태와 양치 후 먹기 편한 정제 형태를 선택할 수 있음</t>
-        </is>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>구미 섭취 후 양치 번거로움 — 젤리 구미 제형의 경우 섭취 후 양치를 다시 해야 하는 소소한 불편함이 있음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6678,58 +6641,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>34,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000142695&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014344ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/A00000014269532ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>12324</v>
+        <v>27992</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>속 편한 장 건강 개선 — 배 아픔이나 가스 차는 증상 없이 배변 활동을 잘 도와줌</t>
+          <t>확실한 에너지 충전 — 과제나 일에 치일 때 먹어주면 덜 피곤하고 기운이 불끈 남</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>높은 보장 균수와 피부 면역 — 보장 균수가 높으며 꾸준히 먹으면 피부 면역 관리에도 도움 됨</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 러기지택 — 산리오 러기지택이 기획으로 제공되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>올인원 영양 배합 — 미량영양소가 배합되어 정제와 액상을 한 번에 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>비싼 가격대 — 다른 비타민 제품에 비해 가격대가 높게 책정됨</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6737,49 +6700,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>판도라</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>24,700원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>41011</v>
+        <v>8922</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 피곤하고 체력이 떨어질 때 복용하면 확실한 활력 충전 효과가 있음</t>
+          <t>간편한 붓기 라인 관리 — 야식이나 짠 음식을 먹은 다음 날 아침 붓기 완화에 도움 됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>탄산수 조합의 상큼함 — 꾸덕한 액상을 시원한 탄산수에 타 마시면 에이드처럼 맛있게 즐길 수 있음</t>
+          <t>물 없이 간편 섭취 — 소형 스틱 액상 포 형태로 물 없이 짜 마시기 편리함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 타 비타민 제품 대비 가격대가 비싸서 지속 구매에 부담이 됨</t>
+          <t>미세한 한약 풍미 — 상큼한 포도맛 베이스이나 끝맛에 은은한 한약 느낌이 섞여 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -6901,29 +6864,29 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
@@ -6936,12 +6899,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -6958,47 +6921,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>그린몬스터</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>바이오렉트라</t>
-        </is>
-      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>그래니샐러드</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>판도라</t>
         </is>
       </c>
     </row>
@@ -7010,52 +6973,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[50억 보장] 그린몬스터 이너블라썸 질 유래 유산균 30캡슐 (1개월분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>바이오렉트라 마그네슘 400 울트라 다이렉트</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>그래니 살라 VPL정 60정(1개월분)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7035,7 @@
         <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.9</v>
@@ -7087,13 +7050,13 @@
         <v>4.9</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7103,34 +7066,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6494</v>
+        <v>5570</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>24945</v>
+        <v>6498</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>14774</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>8078</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>24957</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>3158</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>24129</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>8071</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>267</v>
-      </c>
       <c r="I7" s="3" t="n">
-        <v>10914</v>
+        <v>41013</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14757</v>
+        <v>44</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>12324</v>
+        <v>27992</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>41011</v>
+        <v>8922</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7141,63 +7104,58 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 피로 개선 — 복용 후 아침에 몸이 가뿐해지고 피로 체감이 달라짐
-3000mg 고용량 섭취 — 1포로 고용량 비타민 C 3,000mg을 간편하게 섭취할 수 있음</t>
+          <t>고함량 체력 끌어올림 — 3000mg 고용량으로 신맛이 강하지만 피로 개선 효과가 확실함
+흡수 빠른 가루 제형 — 알약 대비 흡수와 복용이 유용한 가루 형태로 구성됨</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>질과 장 동시 케어 — 질 건강과 장 건강을 한 번에 더블 케어할 수 있어 유용함
-초소형 캡슐의 목넘김 — 170mg의 매우 작고 가벼운 캡슐이라 물과 함께 쉽게 넘어감
-귀여운 포켓몬 굿즈 — 포켓몬 에디션 패키지와 증정 카드케이스의 소장 가치가 높음</t>
+          <t>가뿐한 아침 피로 회복 — 지속 섭취 시 아침에 몸이 가뿐해지고 피로도가 달라짐
+넉넉한 100일분 용량 — 100포 대용량이라 오랫동안 꾸준히 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 합리적 가격 — 비싼 제품과 차이 없이 가격 부담이 적어 정착하기 좋음
-안전한 듀라벡 코팅 — 열과 위산에 강한 코팅 기술로 유산균이 장까지 잘 전달됨</t>
+          <t>빠르고 깊은 수면 유도 — 취침 전 섭취 시 잠이 확 들고 푹 자는 데 도움이 됨
+맛있는 구미 제형 — 약이 아닌 젤리 형태로 간식처럼 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 면역 및 장 건강 — 공복 복용 시 장 건강과 면역력을 관리하는 데 효과를 봄
-알찬 1+1 기획 구성 — 1+1 기획으로 2달 동안 복용 가능한 60캡슐을 확보할 수 있음</t>
+          <t>간편한 1일 1캡슐 — 아침 공복에 물과 함께 하루 한 알로 간편하게 케어함
+질과 장 건강 케어 — 여성 건강 기초가 되는 질유산균과 장 건강을 함께 챙김</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>여성용 질유산균 루틴 — 질 건강 관리를 위한 아침 공복 이너뷰티 루틴으로 적합함
-철분제 추가 증정 — 철분 헤모케어가 증정되어 추가 영양 보충이 가능함</t>
+          <t>소형 캡슐 목넘김 — 170mg의 매우 작은 캡슐 크기라 물과 함께 쉽게 넘어감
+질과 장 더블 케어 — 식약처 인정 원료로 보장균수 50억을 충족하여 효과적임
+귀여운 포켓몬 콜라보 — 카드케이스 증정 등 패키지가 귀여워 소장 가치가 높음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>할인가 구매의 유용성 — 세일 및 쿠폰 혜택을 이용해 저렴하게 쟁여두기 좋음</t>
+          <t>부담 없는 저렴한 가격 — 가격대가 저렴하여 꾸준히 정착해 먹기 좋음
+듀라벡 코팅 기술 — 19종 유산균이 장까지 안전하게 전달되도록 코팅 처리됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 맛과 에너지 충전 — 상큼하게 즐길 수 있어 피로할 때 활력을 채우기 좋음
-포차코 메쉬백 증정 — 귀여운 포차코 메쉬백이 포함되어 구성이 만족스러움</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>빠르고 깊은 수면 유도 — 자기 전 복용 시 깊고 편안하게 잠들 수 있도록 도와줌
-제형 선택의 다양성 — 맛있는 젤리 형태와 양치 후 먹기 편한 정제 형태를 선택할 수 있음</t>
-        </is>
-      </c>
+          <t>즉각적인 체력 충전 — 지칠 때 하나만 챙겨 먹어도 피로 회복 효과가 확실함
+탄산수 활용 복용법 — 진한 액상을 탄산수에 타 마시면 상큼한 에이드처럼 즐길 수 있음</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>속 편한 장 건강 개선 — 배 아픔이나 가스 차는 증상 없이 배변 활동을 잘 도와줌
-높은 보장 균수와 피부 면역 — 보장 균수가 높으며 꾸준히 먹으면 피부 면역 관리에도 도움 됨
-귀여운 산리오 러기지택 — 산리오 러기지택이 기획으로 제공되어 만족스러움</t>
+          <t>확실한 에너지 충전 — 과제나 일에 치일 때 먹어주면 덜 피곤하고 기운이 불끈 남
+올인원 영양 배합 — 미량영양소가 배합되어 정제와 액상을 한 번에 먹기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 체감 — 피곤하고 체력이 떨어질 때 복용하면 확실한 활력 충전 효과가 있음
-탄산수 조합의 상큼함 — 꾸덕한 액상을 시원한 탄산수에 타 마시면 에이드처럼 맛있게 즐길 수 있음</t>
+          <t>간편한 붓기 라인 관리 — 야식이나 짠 음식을 먹은 다음 날 아침 붓기 완화에 도움 됨
+물 없이 간편 섭취 — 소형 스틱 액상 포 형태로 물 없이 짜 마시기 편리함</t>
         </is>
       </c>
     </row>
@@ -7209,24 +7167,36 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>충분한 수분 섭취 필요 — 고용량 제형 특성상 결석 방지를 위해 하루 2L 이상 물을 마셔야 함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>충분한 수구 섭취 필요 — 고용량 복용 특성상 결석 예방을 위해 많은 물을 마셔야 함</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>수분 섭취 유의 — 부작용을 방지하기 위해 하루 2L 이상의 물 섭취가 권장됨</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 섭취 양치 번거로움 — 젤리 형태 특성상 섭취 후 양치를 다시 해야 하는 번거로움이 있음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>구미 섭취 후 양치 번거로움 — 젤리 구미 제형의 경우 섭취 후 양치를 다시 해야 하는 소소한 불편함이 있음</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>높은 가격 부담 — 제품 품질은 좋으나 다소 비싼 가격대가 단점임</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>비싼 가격대 — 다른 비타민 제품에 비해 가격대가 높게 책정됨</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 가격 — 타 비타민 제품 대비 가격대가 비싸서 지속 구매에 부담이 됨</t>
+          <t>미세한 한약 풍미 — 상큼한 포도맛 베이스이나 끝맛에 은은한 한약 느낌이 섞여 있음</t>
         </is>
       </c>
     </row>
@@ -7238,52 +7208,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>9,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>25,900원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>27,400원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>15,900원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>24,320원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>35,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>23,500원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>13,950원</t>
+          <t>34,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>53,900원</t>
+          <t>24,700원</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7409,67 +7379,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
         <v>8</v>
-      </c>
-      <c r="C3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7479,35 +7449,35 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -7519,7 +7489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7529,19 +7499,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7551,10 +7521,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7563,7 +7533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7573,19 +7543,19 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7598,31 +7568,9 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
